--- a/NV_DEMO/Assets/StreamingAssets/Story/1-1.xlsx
+++ b/NV_DEMO/Assets/StreamingAssets/Story/1-1.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
   <si>
     <t>中文姓名</t>
   </si>
@@ -67,13 +66,73 @@
     <t>Character2</t>
   </si>
   <si>
-    <t>安妮</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>Annie</t>
+    <t>...</t>
+  </si>
+  <si>
+    <t>rooftop_Nightscene</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>......</t>
+  </si>
+  <si>
+    <t>一如既往的，繁星铺满了整片夜空。</t>
+  </si>
+  <si>
+    <t>月亮也在那里，安静地挂在浩瀚星海之中，仿佛是宇宙间最温柔的眼眸，注视着天地万象，D城被其清冷的银辉拥住，蒙上了梦幻的面纱。</t>
+  </si>
+  <si>
+    <t>寒意渐起，下意识地竖起领口，试图阻挡这股无孔不入的凉气。</t>
+  </si>
+  <si>
+    <t>风里裹挟着一种特殊的味道。</t>
+  </si>
+  <si>
+    <t>那是潮湿的苔藓气味，是远处江面淡淡的腥气，是劣质炸油在深夜街头弥漫的焦香，混合在一起的气味并不能算作好闻，但莫名让人感到安心。吐出一口白雾，目光漫无目的地在D城里面游走。</t>
+  </si>
+  <si>
+    <t>熟悉感，疏离感，你知道这里的一切，可这座城明明离你那么远。</t>
+  </si>
+  <si>
+    <t>风拂过耳畔，发出一声极轻的、几乎不可闻的嗡鸣，恍惚间，周遭寂静的空气里似乎涌动起了喧嚣的人声——</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>那些声音太吵了，却又真实地让你感到一种几乎窒息的怀念。</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>「喂，[Name]，别睡了！」</t>
+  </si>
+  <si>
+    <t>「别睡了，别睡了，快起来！」</t>
+  </si>
+  <si>
+    <t>——看来是放学了，又是不知道干了什么的一天。</t>
+  </si>
+  <si>
+    <t>一只手重重地拍在了我的肩膀上。 想都不用想，一定是张杨。</t>
+  </si>
+  <si>
+    <t>张杨</t>
+  </si>
+  <si>
+    <t>「发什么呆呢？喊你两声了。走啊，好不容易挨到了周五下课，咱们去老街吃炸串去。」</t>
+  </si>
+  <si>
+    <t>zhangYang_excited</t>
+  </si>
+  <si>
+    <t>classroom_Dusk</t>
   </si>
   <si>
     <t>appearAt</t>
@@ -82,19 +141,205 @@
     <t>[Name]</t>
   </si>
   <si>
+    <t>「你又要翘晚自习？」</t>
+  </si>
+  <si>
+    <t>「搞得好像你天天认真学习一样。」</t>
+  </si>
+  <si>
+    <t>zhangYang_serious</t>
+  </si>
+  <si>
+    <t>张杨毫不在意地耸了耸肩，手已经熟练地搭上了我的书包带子，往走廊方向一拽，动作自然得像是演练过无数次。</t>
+  </si>
+  <si>
+    <t>「走吧走吧，今天周五。」</t>
+  </si>
+  <si>
+    <t>zhangYang_normal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>他说这话的时候语气带着一种理所当然的笃定，好像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>本身就足以成为一切行为的正当理由。</t>
+    </r>
+  </si>
+  <si>
+    <t>走廊里已经热闹起来了。</t>
+  </si>
+  <si>
+    <t>classroomoutside_Dusk</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>楼梯也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已经挤满了人，有人笑着推搡，有人一边往外走一边抱怨作业，脚步声在水泥地上连成一片。天色还没完全暗下去，夕阳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的光线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从教学楼的缝隙里斜斜地照进来，灰尘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>照得清清楚楚。</t>
+    </r>
+  </si>
+  <si>
+    <t>schoolstairs_Dusk</t>
+  </si>
+  <si>
+    <t>「老街那家炸串，今天的东西肯定好吃。」张杨一边走一边说，「我下午路过的时候看见他们在备料，食材肯定新鲜。」</t>
+  </si>
+  <si>
+    <t>zhangYang_smile</t>
+  </si>
+  <si>
+    <t>「观察很仔细嘛。」</t>
+  </si>
+  <si>
+    <t>「这叫生活情报。」他一本正经地回答，又凑近了一点，压低声音，「而且我今天有正事要跟你说。」</t>
+  </si>
+  <si>
+    <t>我瞥了他一眼。</t>
+  </si>
+  <si>
+    <t>「你哪次找我不是“有正事”？」</t>
+  </si>
+  <si>
+    <t>「...这次不一样。」</t>
+  </si>
+  <si>
+    <t>他说完又卖了个关子，偏偏不继续往下讲，只是脚步明显快了几分，像是生怕我临时反悔。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>出了校门，风迎面吹过来，带着点傍晚特有的凉意。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>城的天总是暗得很慢，街道两侧的店铺陆续亮起灯来，老旧的招牌在暮色里显得有些模糊，却又看着让人安心。</t>
+    </r>
+  </si>
+  <si>
+    <t>school_Dusk</t>
+  </si>
+  <si>
+    <t>今天翘晚自习的学生格外多。</t>
+  </si>
+  <si>
+    <t>周五、老街、炸串。</t>
+  </si>
+  <si>
+    <t>平凡得不能再平凡，却又让人下意识地不想错过。</t>
+  </si>
+  <si>
+    <t>goto</t>
+  </si>
+  <si>
     <t>1-2</t>
-  </si>
-  <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>End of story</t>
   </si>
 </sst>
 </file>
@@ -107,13 +352,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -258,6 +509,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -580,145 +843,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1031,14 +1303,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="50.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="28.375" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -1071,104 +1351,297 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1"/>
-      <c r="N1" s="1"/>
-      <c r="O1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="3" spans="1:12">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2">
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25" spans="1:12">
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" ht="38.25" spans="1:12">
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5" spans="1:12">
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="25.5" spans="1:12">
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="27" spans="1:9">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="1"/>
-      <c r="O2"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3"/>
-      <c r="N3" s="1"/>
-      <c r="O3"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="N4" s="1"/>
-      <c r="O4"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="1"/>
-      <c r="P6" s="1"/>
+      <c r="I19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" ht="25.5" spans="1:9">
+      <c r="B22" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" ht="26.25" spans="1:9">
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="B25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" ht="51" spans="1:9">
+      <c r="B26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" ht="40.5" spans="1:9">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" ht="27" spans="1:9">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="B30" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" ht="25.5" spans="1:5">
+      <c r="B33" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" ht="39.75" spans="1:5">
+      <c r="B34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="B36" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="B37" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1187,16 +1660,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/NV_DEMO/Assets/StreamingAssets/Story/1-1.xlsx
+++ b/NV_DEMO/Assets/StreamingAssets/Story/1-1.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
   <si>
     <t>中文姓名</t>
   </si>
@@ -66,6 +66,18 @@
     <t>Character2</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>idTo</t>
+  </si>
+  <si>
+    <t>Char1Anim</t>
+  </si>
+  <si>
+    <t>Char2Anim</t>
+  </si>
+  <si>
     <t>...</t>
   </si>
   <si>
@@ -90,7 +102,10 @@
     <t>风里裹挟着一种特殊的味道。</t>
   </si>
   <si>
-    <t>那是潮湿的苔藓气味，是远处江面淡淡的腥气，是劣质炸油在深夜街头弥漫的焦香，混合在一起的气味并不能算作好闻，但莫名让人感到安心。吐出一口白雾，目光漫无目的地在D城里面游走。</t>
+    <t>那是潮湿的苔藓气味，是远处江面淡淡的腥气，是劣质炸油在深夜街头弥漫的焦香，混合在一起的气味并不能算作好闻，但莫名让人感到安心。</t>
+  </si>
+  <si>
+    <t>吐出一口白雾，目光漫无目的地在D城里面游走。</t>
   </si>
   <si>
     <t>熟悉感，疏离感，你知道这里的一切，可这座城明明离你那么远。</t>
@@ -99,15 +114,15 @@
     <t>风拂过耳畔，发出一声极轻的、几乎不可闻的嗡鸣，恍惚间，周遭寂静的空气里似乎涌动起了喧嚣的人声——</t>
   </si>
   <si>
-    <t>classroom</t>
-  </si>
-  <si>
     <t>那些声音太吵了，却又真实地让你感到一种几乎窒息的怀念。</t>
   </si>
   <si>
     <t>black</t>
   </si>
   <si>
+    <t>Go Back 2 This Town</t>
+  </si>
+  <si>
     <t>？？？</t>
   </si>
   <si>
@@ -138,6 +153,9 @@
     <t>appearAt</t>
   </si>
   <si>
+    <t>JUMP</t>
+  </si>
+  <si>
     <t>[Name]</t>
   </si>
   <si>
@@ -150,13 +168,40 @@
     <t>zhangYang_serious</t>
   </si>
   <si>
+    <t>「快点啊，再迟一点就没位置坐了。」</t>
+  </si>
+  <si>
+    <t>zhangYang_angry</t>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>好吧|想回家躺着|我还想上晚自习呢</t>
+  </si>
+  <si>
+    <t>24|25|26</t>
+  </si>
+  <si>
+    <t>「Let's go！」</t>
+  </si>
+  <si>
+    <t>「吃完再回家躺去，接下来你还能躺两天呢。」</t>
+  </si>
+  <si>
+    <t>「...你觉得我会信吗？」</t>
+  </si>
+  <si>
+    <t>zhangyang_confused</t>
+  </si>
+  <si>
     <t>张杨毫不在意地耸了耸肩，手已经熟练地搭上了我的书包带子，往走廊方向一拽，动作自然得像是演练过无数次。</t>
   </si>
   <si>
-    <t>「走吧走吧，今天周五。」</t>
-  </si>
-  <si>
-    <t>zhangYang_normal</t>
+    <t>「正好今天周五。」</t>
+  </si>
+  <si>
+    <t>zhangYang_smile</t>
   </si>
   <si>
     <r>
@@ -274,13 +319,19 @@
     <t>「老街那家炸串，今天的东西肯定好吃。」张杨一边走一边说，「我下午路过的时候看见他们在备料，食材肯定新鲜。」</t>
   </si>
   <si>
-    <t>zhangYang_smile</t>
-  </si>
-  <si>
     <t>「观察很仔细嘛。」</t>
   </si>
   <si>
-    <t>「这叫生活情报。」他一本正经地回答，又凑近了一点，压低声音，「而且我今天有正事要跟你说。」</t>
+    <t>「这叫生活情报。」</t>
+  </si>
+  <si>
+    <t>zhangYang_normal</t>
+  </si>
+  <si>
+    <t>他一本正经地回答，又凑近了一点，压低声音。</t>
+  </si>
+  <si>
+    <t>「而且我今天有正事要跟你说。」</t>
   </si>
   <si>
     <t>我瞥了他一眼。</t>
@@ -513,13 +564,13 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1303,18 +1354,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="50.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="22.5" customWidth="1"/>
-    <col min="6" max="6" width="28.375" customWidth="1"/>
-    <col min="9" max="9" width="21.25" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="8" max="8" width="1.25" customWidth="1"/>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
+    <col min="11" max="11" width="1.875" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,296 +1404,546 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25" spans="1:16">
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5" spans="1:16">
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="38.25" spans="1:16">
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="25.5" spans="1:16">
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="38.25" spans="1:16">
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="25.5" spans="1:16">
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="M14">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="M15">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="B3" s="1" t="s">
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="M16">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="2" t="s">
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17">
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="38.25" spans="1:12">
-      <c r="B5" s="2" t="s">
+    <row r="18" spans="1:15">
+      <c r="B18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="2" t="s">
+    <row r="19" ht="25.5" spans="1:15">
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M19">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="38.25" spans="1:12">
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5" spans="1:12">
-      <c r="B9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5" spans="1:12">
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3"/>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="B18" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="27" spans="1:9">
-      <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+    <row r="20" ht="27" spans="1:15">
       <c r="A20" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20">
+        <v>19</v>
+      </c>
+      <c r="O20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1" spans="1:15">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="M22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" t="s">
+        <v>47</v>
+      </c>
+      <c r="M23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>38</v>
+      </c>
+      <c r="M25">
+        <v>24</v>
+      </c>
+      <c r="N25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26">
+        <v>25</v>
+      </c>
+      <c r="N26">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27">
+        <v>26</v>
+      </c>
+      <c r="N27">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" ht="38.25" spans="1:15">
+      <c r="B28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="26.25" spans="1:15">
+      <c r="B30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="B31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="51" spans="1:15">
+      <c r="B32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>62</v>
+      </c>
+      <c r="M32">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="33" ht="40.5" spans="1:13">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" t="s">
+        <v>66</v>
+      </c>
+      <c r="M35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="B36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="M36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="B37" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="B38" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M39">
         <v>38</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" t="s">
+        <v>45</v>
+      </c>
+      <c r="M40">
         <v>39</v>
       </c>
-      <c r="I21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" ht="25.5" spans="1:9">
-      <c r="B22" s="2" t="s">
+    </row>
+    <row r="41" ht="25.5" spans="1:13">
+      <c r="B41" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M41">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="42" ht="52.5" spans="1:13">
+      <c r="B42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" t="s">
+        <v>74</v>
+      </c>
+      <c r="M42">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="43" spans="1:13">
+      <c r="B43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M43">
         <v>42</v>
       </c>
-      <c r="I23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" ht="26.25" spans="1:9">
-      <c r="B24" s="4" t="s">
+    </row>
+    <row r="44" spans="1:13">
+      <c r="B44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="B25" s="5" t="s">
+    <row r="45" spans="1:13">
+      <c r="B45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M45">
         <v>44</v>
       </c>
-      <c r="E25" t="s">
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M46">
         <v>45</v>
-      </c>
-    </row>
-    <row r="26" ht="51" spans="1:9">
-      <c r="B26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" ht="40.5" spans="1:9">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" ht="27" spans="1:9">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="B30" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" ht="25.5" spans="1:5">
-      <c r="B33" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" ht="39.75" spans="1:5">
-      <c r="B34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="B35" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="B36" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="B37" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
